--- a/tungfamLoanForms.xlsx
+++ b/tungfamLoanForms.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <workbookPr filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3600" windowWidth="20640" windowHeight="11760"/>
   </bookViews>
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">cardFront!$A$1:$B$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">CardPayment!$A$1:$H$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">loanForm!$A$1:$B$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">loanForm!$A$1:$B$28</definedName>
   </definedNames>
   <calcPr calcId="124519" iterateDelta="1E-4"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>Name:</t>
   </si>
@@ -68,12 +68,30 @@
   </si>
   <si>
     <t>Mobile:</t>
+  </si>
+  <si>
+    <t>Use of loan</t>
+  </si>
+  <si>
+    <t>Existing Loans</t>
+  </si>
+  <si>
+    <t>Daily/Weekly sales</t>
+  </si>
+  <si>
+    <t>Daily/Weekly profit</t>
+  </si>
+  <si>
+    <t>Profit Margin</t>
+  </si>
+  <si>
+    <t>Existing Payments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -160,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -176,9 +194,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -221,13 +236,13 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>95252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>4226152</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:colOff>3016250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>57745</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -250,8 +265,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="95250"/>
-          <a:ext cx="5331052" cy="2000250"/>
+          <a:off x="0" y="95252"/>
+          <a:ext cx="4524375" cy="1692868"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -567,7 +582,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -575,138 +590,161 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B31"/>
+  <dimension ref="A2:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="22.5703125" style="1" customWidth="1"/>
     <col min="2" max="2" width="64.42578125" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
     </row>
+    <row r="6" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4"/>
+    </row>
     <row r="7" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="B8" s="4"/>
     </row>
     <row r="9" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B9" s="4"/>
     </row>
     <row r="10" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B10" s="4"/>
     </row>
     <row r="11" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4"/>
     </row>
     <row r="12" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4"/>
     </row>
     <row r="13" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4"/>
     </row>
     <row r="16" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="4"/>
+    </row>
+    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4"/>
+    </row>
+    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4"/>
+    </row>
+    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="4"/>
+    </row>
+    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+    </row>
+    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="3"/>
-    </row>
-    <row r="17" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="B21" s="3"/>
+    </row>
+    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="9"/>
-    </row>
-    <row r="18" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-    </row>
-    <row r="20" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="B22" s="8"/>
+    </row>
+    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="9"/>
-    </row>
-    <row r="22" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-    </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="B24" s="8"/>
+    </row>
+    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+    </row>
+    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="4"/>
-    </row>
-    <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-    </row>
-    <row r="25" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="B26" s="4"/>
     </row>
     <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="4"/>
+    </row>
+    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="4"/>
-    </row>
-    <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-    </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+    </row>
     <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:B24"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -730,8 +768,8 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:2" ht="91.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
     </row>
     <row r="4" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -814,556 +852,556 @@
   <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" style="8" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" style="8" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="27.42578125" style="8" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="5.42578125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="5.42578125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" style="7" customWidth="1"/>
+    <col min="8" max="8" width="27.42578125" style="7" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7">
+      <c r="A1" s="6">
         <v>1</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6">
         <v>31</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7">
+      <c r="D1" s="6"/>
+      <c r="E1" s="6">
         <v>61</v>
       </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7">
+      <c r="F1" s="6"/>
+      <c r="G1" s="6">
         <v>91</v>
       </c>
-      <c r="H1" s="7"/>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7">
+      <c r="A2" s="6">
         <v>2</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6">
         <v>32</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7">
+      <c r="D2" s="6"/>
+      <c r="E2" s="6">
         <v>62</v>
       </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7">
+      <c r="F2" s="6"/>
+      <c r="G2" s="6">
         <v>92</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="6">
         <v>3</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6">
         <v>33</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6">
         <v>63</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7">
+      <c r="F3" s="6"/>
+      <c r="G3" s="6">
         <v>93</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>4</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6">
         <v>34</v>
       </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7">
+      <c r="D4" s="6"/>
+      <c r="E4" s="6">
         <v>64</v>
       </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7">
+      <c r="F4" s="6"/>
+      <c r="G4" s="6">
         <v>94</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>5</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6">
         <v>35</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
         <v>65</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7">
+      <c r="F5" s="6"/>
+      <c r="G5" s="6">
         <v>95</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>6</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6">
         <v>36</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7">
+      <c r="D6" s="6"/>
+      <c r="E6" s="6">
         <v>66</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6">
         <v>96</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>7</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7">
+      <c r="B7" s="6"/>
+      <c r="C7" s="6">
         <v>37</v>
       </c>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>67</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7">
+      <c r="F7" s="6"/>
+      <c r="G7" s="6">
         <v>97</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>8</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7">
+      <c r="B8" s="6"/>
+      <c r="C8" s="6">
         <v>38</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7">
+      <c r="D8" s="6"/>
+      <c r="E8" s="6">
         <v>68</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6">
         <v>98</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7">
+      <c r="B9" s="6"/>
+      <c r="C9" s="6">
         <v>39</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7">
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
         <v>69</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7">
+      <c r="F9" s="6"/>
+      <c r="G9" s="6">
         <v>99</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>10</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7">
+      <c r="B10" s="6"/>
+      <c r="C10" s="6">
         <v>40</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6">
         <v>70</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
+      <c r="F10" s="6"/>
+      <c r="G10" s="6">
         <v>100</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>11</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6">
         <v>41</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7">
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
         <v>71</v>
       </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6">
         <v>101</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>12</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7">
+      <c r="B12" s="6"/>
+      <c r="C12" s="6">
         <v>42</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7">
+      <c r="D12" s="6"/>
+      <c r="E12" s="6">
         <v>72</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7">
+      <c r="F12" s="6"/>
+      <c r="G12" s="6">
         <v>102</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>13</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7">
+      <c r="B13" s="6"/>
+      <c r="C13" s="6">
         <v>43</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7">
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
         <v>73</v>
       </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6">
         <v>103</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>14</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6">
         <v>44</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6">
         <v>74</v>
       </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
+      <c r="F14" s="6"/>
+      <c r="G14" s="6">
         <v>104</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>15</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7">
+      <c r="B15" s="6"/>
+      <c r="C15" s="6">
         <v>45</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6">
         <v>75</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7">
+      <c r="F15" s="6"/>
+      <c r="G15" s="6">
         <v>105</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>16</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7">
+      <c r="B16" s="6"/>
+      <c r="C16" s="6">
         <v>46</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6">
         <v>76</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7">
+      <c r="F16" s="6"/>
+      <c r="G16" s="6">
         <v>106</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
+      <c r="A17" s="6">
         <v>17</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7">
+      <c r="B17" s="6"/>
+      <c r="C17" s="6">
         <v>47</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7">
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
         <v>77</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7">
+      <c r="F17" s="6"/>
+      <c r="G17" s="6">
         <v>107</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
+      <c r="A18" s="6">
         <v>18</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7">
+      <c r="B18" s="6"/>
+      <c r="C18" s="6">
         <v>48</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6">
         <v>78</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7">
+      <c r="F18" s="6"/>
+      <c r="G18" s="6">
         <v>108</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
+      <c r="A19" s="6">
         <v>19</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7">
+      <c r="B19" s="6"/>
+      <c r="C19" s="6">
         <v>49</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7">
+      <c r="D19" s="6"/>
+      <c r="E19" s="6">
         <v>79</v>
       </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7">
+      <c r="F19" s="6"/>
+      <c r="G19" s="6">
         <v>109</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
+      <c r="A20" s="6">
         <v>20</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7">
+      <c r="B20" s="6"/>
+      <c r="C20" s="6">
         <v>50</v>
       </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6">
         <v>80</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7">
+      <c r="F20" s="6"/>
+      <c r="G20" s="6">
         <v>110</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
+      <c r="A21" s="6">
         <v>21</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6">
         <v>51</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6">
         <v>81</v>
       </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7">
+      <c r="F21" s="6"/>
+      <c r="G21" s="6">
         <v>111</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+      <c r="A22" s="6">
         <v>22</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6">
         <v>52</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7">
+      <c r="D22" s="6"/>
+      <c r="E22" s="6">
         <v>82</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7">
+      <c r="F22" s="6"/>
+      <c r="G22" s="6">
         <v>112</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="7">
+      <c r="A23" s="6">
         <v>23</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6">
         <v>53</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6">
         <v>83</v>
       </c>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7">
+      <c r="F23" s="6"/>
+      <c r="G23" s="6">
         <v>113</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="7">
+      <c r="A24" s="6">
         <v>24</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6">
         <v>54</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7">
+      <c r="D24" s="6"/>
+      <c r="E24" s="6">
         <v>84</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6">
         <v>114</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
+      <c r="A25" s="6">
         <v>25</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6">
         <v>55</v>
       </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6">
         <v>85</v>
       </c>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7">
+      <c r="F25" s="6"/>
+      <c r="G25" s="6">
         <v>115</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
+      <c r="A26" s="6">
         <v>26</v>
       </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6">
         <v>56</v>
       </c>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7">
+      <c r="D26" s="6"/>
+      <c r="E26" s="6">
         <v>86</v>
       </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7">
+      <c r="F26" s="6"/>
+      <c r="G26" s="6">
         <v>116</v>
       </c>
-      <c r="H26" s="7"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7">
+      <c r="A27" s="6">
         <v>27</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6">
         <v>57</v>
       </c>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6">
         <v>87</v>
       </c>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7">
+      <c r="F27" s="6"/>
+      <c r="G27" s="6">
         <v>117</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="7">
+      <c r="A28" s="6">
         <v>28</v>
       </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6">
         <v>58</v>
       </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7">
+      <c r="D28" s="6"/>
+      <c r="E28" s="6">
         <v>88</v>
       </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7">
+      <c r="F28" s="6"/>
+      <c r="G28" s="6">
         <v>118</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="7">
+      <c r="A29" s="6">
         <v>29</v>
       </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6">
         <v>59</v>
       </c>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6">
         <v>89</v>
       </c>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7">
+      <c r="F29" s="6"/>
+      <c r="G29" s="6">
         <v>119</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="7">
+      <c r="A30" s="6">
         <v>30</v>
       </c>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6">
         <v>60</v>
       </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7">
+      <c r="D30" s="6"/>
+      <c r="E30" s="6">
         <v>90</v>
       </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7">
+      <c r="F30" s="6"/>
+      <c r="G30" s="6">
         <v>120</v>
       </c>
-      <c r="H30" s="7"/>
+      <c r="H30" s="6"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>

--- a/tungfamLoanForms.xlsx
+++ b/tungfamLoanForms.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
-  <workbookPr filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3600" windowWidth="20640" windowHeight="11760"/>
   </bookViews>
@@ -14,9 +14,9 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">cardFront!$A$1:$B$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">CardPayment!$A$1:$H$30</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">loanForm!$A$1:$B$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">loanForm!$A$1:$B$29</definedName>
   </definedNames>
-  <calcPr calcId="124519" iterateDelta="1E-4"/>
+  <calcPr calcId="124519"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>Name:</t>
   </si>
@@ -86,12 +86,15 @@
   </si>
   <si>
     <t>Existing Payments</t>
+  </si>
+  <si>
+    <t>Witness Signature</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -273,6 +276,80 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2746375</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>4206875</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4254500" y="111125"/>
+          <a:ext cx="1460500" cy="1698625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent6"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent6"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1600" b="0" cap="none" spc="0">
+              <a:ln w="0"/>
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="38100" dist="19050" dir="2700000" algn="tl" rotWithShape="0">
+                  <a:schemeClr val="dk1">
+                    <a:alpha val="40000"/>
+                  </a:schemeClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>photo</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -582,7 +659,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -590,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B32"/>
+  <dimension ref="A2:B33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.5703125" style="1" customWidth="1"/>
@@ -689,7 +766,7 @@
       </c>
       <c r="B19" s="4"/>
     </row>
-    <row r="20" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
     </row>
@@ -705,14 +782,14 @@
       </c>
       <c r="B22" s="8"/>
     </row>
-    <row r="23" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:2" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="24" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B24" s="8"/>
     </row>
-    <row r="25" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
     </row>
@@ -724,23 +801,29 @@
     </row>
     <row r="27" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B27" s="4"/>
     </row>
     <row r="28" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="4"/>
+    </row>
+    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B28" s="4"/>
-    </row>
-    <row r="29" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-    </row>
-    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B29" s="4"/>
+    </row>
+    <row r="30" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+    </row>
     <row r="31" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:2" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A22:B22"/>
